--- a/out/MLP-mamba2_repeat_4_000005.xlsx
+++ b/out/MLP-mamba2_repeat_4_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.443095189965484</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.443095189965484</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.414642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.414642784948225</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.414642784948225</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.414642784948225</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.414642784948225</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.414642784948225</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.414642784948225</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8430951899654835</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.014642784948225</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8430951899654835</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.443095189965484</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.414642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.443095189965484</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.443095189965484</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.414642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8430951899654835</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.014642784948225</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.014642784948225</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.443095189965484</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.443095189965484</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_4_000005.xlsx
+++ b/out/MLP-mamba2_repeat_4_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.414642784948225</v>
+        <v>0.4825578011270781</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.414642784948225</v>
+        <v>0.4825578011270781</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.414642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.414642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.6238367016906173</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.6238367016906173</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.414642784948225</v>
+        <v>0.4825578011270781</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.6238367016906173</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.014642784948225</v>
+        <v>0.4825578011270781</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_4_000005.xlsx
+++ b/out/MLP-mamba2_repeat_4_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4315330982208252</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7200000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4253272116184235</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.8410568833351135</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4825578011270781</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5804972648620605</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.6825578011270782</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4127922058105469</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.645527720451355</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.8468140959739685</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.1863635033369064</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.02936054971823043</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4031557738780975</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.231375440955162</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.5852788090705872</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.260389506816864</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.396147608757019</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.2640741169452667</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.2747582495212555</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.849101185798645</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.7259734272956848</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.335755052535926</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.8296814560890198</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.3270463049411774</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.721538245677948</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.1282102018594742</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.02936054971823043</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.1294435560703278</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3179389238357544</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.7575934529304504</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4825578011270781</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.5698589682579041</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6825578011270782</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.2930291891098022</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.6825578011270782</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.7028429508209229</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3980793356895447</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.440666139125824</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1706394502817696</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.661349892616272</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.8883448243141174</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.1846222132444382</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.05493633449077606</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1706394502817696</v>
+        <v>0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5719355940818787</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3818534910678864</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.07377553731203079</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.7364757657051086</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.6038072109222412</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.2447068691253662</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.6293737292289734</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.4402523040771484</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>0.4603359401226044</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>0.3749700486660004</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.292831689119339</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5868751406669617</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.3691472709178925</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.4591983556747437</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.3338173031806946</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.297978401184082</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4030193388462067</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1706394502817696</v>
+        <v>0.16</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.6698805093765259</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5308220982551575</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3126486241817474</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.6521886587142944</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.2600921392440796</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.780938446521759</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.2506929934024811</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.6312002539634705</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.5997238159179688</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6825578011270782</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.2735822200775146</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.225552961230278</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3714518249034882</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4014095962047577</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3855703771114349</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3685518205165863</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5514247417449951</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3692793846130371</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3261663019657135</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6238367016906173</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4328807294368744</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.2498074769973755</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.07892080396413803</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.1024628356099129</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.7008192539215088</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.1080438643693924</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.610872745513916</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4787764549255371</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.423127681016922</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6238367016906173</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3318250775337219</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.3</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3956311047077179</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1706394502817696</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.5382278561592102</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.2285842299461365</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.6825578011270782</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.7468413114547729</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.02936054971823043</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4389334321022034</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.790601372718811</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4088892042636871</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.7793245911598206</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.7312731146812439</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.335755052535926</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.6563611626625061</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.3</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.1175036504864693</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.02936054971823043</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.2438340783119202</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4554510116577148</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.2892220914363861</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.7107924818992615</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.4825578011270781</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.5187169909477234</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.335755052535926</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.8429233431816101</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2865192592144012</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.3</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3465116620063782</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4774753749370575</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.469400942325592</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.2182358652353287</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.8686341047286987</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3576553761959076</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.5256173610687256</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.6735345125198364</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.2870706021785736</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4074406027793884</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6238367016906173</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.2829557359218597</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.2760681211948395</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3397344052791595</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2166192829608917</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.287251204252243</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2890336215496063</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.8980890512466431</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.1684000194072723</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.9402706623077393</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.64129638671875</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.335755052535926</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.7811809778213501</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.6871029734611511</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.5013318061828613</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.7234613299369812</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.335755052535926</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.9521493315696716</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.7502028346061707</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.7391613125801086</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.4825578011270781</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.06269853562116623</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.6500000000000004</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.2678740620613098</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-1</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_4_000005.xlsx
+++ b/out/MLP-mamba2_repeat_4_000005.xlsx
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.4253272116184235</v>
+        <v>0.4253272712230682</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.58</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.645527720451355</v>
+        <v>0.6455276608467102</v>
       </c>
       <c r="JB7" t="n">
         <v>0.4399999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.8468140959739685</v>
+        <v>0.8468141555786133</v>
       </c>
       <c r="JB8" t="n">
         <v>0.1600000000000001</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.1863635033369064</v>
+        <v>0.18636354804039</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.4399999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.4031557738780975</v>
+        <v>0.4031558036804199</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.5799999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.396147608757019</v>
+        <v>0.3961475789546967</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.8599999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.2747582495212555</v>
+        <v>0.2747581899166107</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.7259734272956848</v>
+        <v>0.72597336769104</v>
       </c>
       <c r="JB18" t="n">
         <v>0.4399999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.3270463049411774</v>
+        <v>0.327046275138855</v>
       </c>
       <c r="JB20" t="n">
         <v>0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.1294435560703278</v>
+        <v>0.1294435858726501</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.05493633449077606</v>
+        <v>0.05493636056780815</v>
       </c>
       <c r="JB34" t="n">
         <v>0.16</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.3749700486660004</v>
+        <v>0.3749699890613556</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.292831689119339</v>
+        <v>0.2928316593170166</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.7199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.3691472709178925</v>
+        <v>0.3691472411155701</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.3338173031806946</v>
+        <v>0.333817332983017</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.8599999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.297978401184082</v>
+        <v>0.2979783415794373</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.5799999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.6698805093765259</v>
+        <v>0.6698804497718811</v>
       </c>
       <c r="JB52" t="n">
         <v>0.1600000000000001</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.5308220982551575</v>
+        <v>0.5308220386505127</v>
       </c>
       <c r="JB53" t="n">
         <v>0.4399999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.6521886587142944</v>
+        <v>0.6521885991096497</v>
       </c>
       <c r="JB55" t="n">
         <v>0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.2506929934024811</v>
+        <v>0.2506930232048035</v>
       </c>
       <c r="JB58" t="n">
         <v>0.3</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.6312002539634705</v>
+        <v>0.6312003135681152</v>
       </c>
       <c r="JB59" t="n">
         <v>0.3</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.5997238159179688</v>
+        <v>0.5997238755226135</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.5799999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.225552961230278</v>
+        <v>0.2255529910326004</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.8599999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.3855703771114349</v>
+        <v>0.3855704069137573</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.3685518205165863</v>
+        <v>0.3685517907142639</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.3261663019657135</v>
+        <v>0.3261663317680359</v>
       </c>
       <c r="JB69" t="n">
         <v>0.02000000000000007</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.4328807294368744</v>
+        <v>0.4328806400299072</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.2599999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.2498074769973755</v>
+        <v>0.2498075067996979</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.2599999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.7008192539215088</v>
+        <v>0.7008193135261536</v>
       </c>
       <c r="JB74" t="n">
         <v>0.1600000000000001</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.1080438643693924</v>
+        <v>0.108043909072876</v>
       </c>
       <c r="JB75" t="n">
         <v>0.4399999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.610872745513916</v>
+        <v>0.6108728051185608</v>
       </c>
       <c r="JB76" t="n">
         <v>0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.4787764549255371</v>
+        <v>0.4787765741348267</v>
       </c>
       <c r="JB77" t="n">
         <v>0.4399999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.423127681016922</v>
+        <v>0.4231278598308563</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.3318250775337219</v>
+        <v>0.3318251669406891</v>
       </c>
       <c r="JB79" t="n">
         <v>0.3</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.3956311047077179</v>
+        <v>0.3956311643123627</v>
       </c>
       <c r="JB80" t="n">
         <v>0.02000000000000007</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.5382278561592102</v>
+        <v>0.5382279753684998</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.5799999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.2285842299461365</v>
+        <v>0.2285842895507812</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.3</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.7468413114547729</v>
+        <v>0.7468414306640625</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.4389334321022034</v>
+        <v>0.4389335811138153</v>
       </c>
       <c r="JB84" t="n">
         <v>0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.4088892042636871</v>
+        <v>0.4088892638683319</v>
       </c>
       <c r="JB86" t="n">
         <v>0.7199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.7793245911598206</v>
+        <v>0.7793247103691101</v>
       </c>
       <c r="JB87" t="n">
         <v>0.7199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.7312731146812439</v>
+        <v>0.7312731742858887</v>
       </c>
       <c r="JB88" t="n">
         <v>0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.6563611626625061</v>
+        <v>0.6563612222671509</v>
       </c>
       <c r="JB89" t="n">
         <v>0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.1175036504864693</v>
+        <v>0.1175037026405334</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.2438340783119202</v>
+        <v>0.2438341528177261</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.5799999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.4554510116577148</v>
+        <v>0.4554511308670044</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.2892220914363861</v>
+        <v>0.2892221212387085</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.3</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.7107924818992615</v>
+        <v>0.7107925415039062</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.02000000000000007</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.5187169909477234</v>
+        <v>0.5187170505523682</v>
       </c>
       <c r="JB95" t="n">
         <v>0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.2865192592144012</v>
+        <v>0.286519318819046</v>
       </c>
       <c r="JB97" t="n">
         <v>0.3</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.3465116620063782</v>
+        <v>0.3465117812156677</v>
       </c>
       <c r="JB98" t="n">
         <v>0.16</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.4774753749370575</v>
+        <v>0.4774754047393799</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.2182358652353287</v>
+        <v>0.2182359099388123</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.3576553761959076</v>
+        <v>0.3576554954051971</v>
       </c>
       <c r="JB103" t="n">
         <v>0.4399999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.5256173610687256</v>
+        <v>0.5256174206733704</v>
       </c>
       <c r="JB104" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.6735345125198364</v>
+        <v>0.6735345721244812</v>
       </c>
       <c r="JB105" t="n">
         <v>0.1600000000000001</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.2870706021785736</v>
+        <v>0.287070631980896</v>
       </c>
       <c r="JB106" t="n">
         <v>0.16</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.4074406027793884</v>
+        <v>0.4074406921863556</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.2829557359218597</v>
+        <v>0.2829558551311493</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.2760681211948395</v>
+        <v>0.2760681807994843</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3397344052791595</v>
+        <v>0.3397344648838043</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.2166192829608917</v>
+        <v>0.2166193276643753</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.287251204252243</v>
+        <v>0.2872512340545654</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.2890336215496063</v>
+        <v>0.2890336811542511</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.7199999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.1684000194072723</v>
+        <v>0.1684000492095947</v>
       </c>
       <c r="JB115" t="n">
         <v>0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.64129638671875</v>
+        <v>0.6412966847419739</v>
       </c>
       <c r="JB117" t="n">
         <v>0.5799999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.7811809778213501</v>
+        <v>0.7811814546585083</v>
       </c>
       <c r="JB118" t="n">
         <v>0.8599999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.6871029734611511</v>
+        <v>0.6871030330657959</v>
       </c>
       <c r="JB119" t="n">
         <v>0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.5013318061828613</v>
+        <v>0.5013319253921509</v>
       </c>
       <c r="JB120" t="n">
         <v>0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.7234613299369812</v>
+        <v>0.7234614491462708</v>
       </c>
       <c r="JB121" t="n">
         <v>0.5799999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.9521493315696716</v>
+        <v>0.9521494507789612</v>
       </c>
       <c r="JB122" t="n">
         <v>0.7199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.7502028346061707</v>
+        <v>0.7502028942108154</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.16</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.7391613125801086</v>
+        <v>0.7391613721847534</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.2678740620613098</v>
+        <v>0.2678741216659546</v>
       </c>
       <c r="JB126" t="n">
         <v>-1</v>
